--- a/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week03_14Sep.xlsx
+++ b/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week03_14Sep.xlsx
@@ -1073,7 +1073,7 @@
     <row r="8" ht="33.75" customHeight="1" s="42">
       <c r="A8" s="50" t="inlineStr">
         <is>
-          <t>SMSC/BV this week: Build RE begins the festivals-of-light block (Diwali) — pre-teaching ahead of the November festival; makes start the Festivals-of-Light display (EFL: cultural).  PSHE's real class vote = democracy in action — log in the BV hub.  PREP: International Day of Peace is Monday of next week.</t>
+          <t>SMSC/BV this week: Build RE begins the festivals-of-light block (Diwali) — pre-teaching ahead of the November festival; makes start the Festivals-of-Light display (evidence platform: cultural).  PSHE's real class vote = democracy in action — log in the BV hub.  PREP: International Day of Peace is Monday of next week.</t>
         </is>
       </c>
       <c r="B8" s="51" t="n"/>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="I12" s="56" t="inlineStr">
         <is>
-          <t>TA draws round pupils who want it and manages the floor space. Teacher touches their own bone every time a name is said — mirror learning. LOOP [Feedback Policy]: Voice = point/place the label/say the name [VF, ?] → Audience: name one bone back; [R] once received → EVIDENCE: labelled outline photo, upload same day [E: science — daily EFL; banks ELC 8939].</t>
+          <t>TA draws round pupils who want it and manages the floor space. Teacher touches their own bone every time a name is said — mirror learning. LOOP [Feedback Policy]: Voice = point/place the label/say the name [VF, ?] → Audience: name one bone back; [R] once received → EVIDENCE: labelled outline photo, upload same day [E: science — daily evidence platform; banks ELC 8939].</t>
         </is>
       </c>
       <c r="J12" s="56" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="I13" s="59" t="inlineStr">
         <is>
-          <t>TA runs the booth and supports the tally.  LOOP [Feedback Policy]: Voice = pitch/vote/count [VF] → Audience: name the fair-vote rule back; [R] once used for real → EVIDENCE: photos + clip, same day [E: BV democracy — daily EFL; banks AQA UAS].</t>
+          <t>TA runs the booth and supports the tally.  LOOP [Feedback Policy]: Voice = pitch/vote/count [VF] → Audience: name the fair-vote rule back; [R] once used for real → EVIDENCE: photos + clip, same day [E: BV democracy — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J13" s="59" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="I14" s="56" t="inlineStr">
         <is>
-          <t>TA runs the rotation and records each clip.  LOOP [Feedback Policy]: Voice = make + 15-sec clip [VF] → Audience: listen fully before tagging, then [R] → EVIDENCE: make photo + clip to the display, same day [E: cultural — daily EFL].</t>
+          <t>TA runs the rotation and records each clip.  LOOP [Feedback Policy]: Voice = make + 15-sec clip [VF] → Audience: listen fully before tagging, then [R] → EVIDENCE: make photo + clip to the display, same day [E: cultural — daily evidence platform].</t>
         </is>
       </c>
       <c r="J14" s="56" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="I15" s="56" t="inlineStr">
         <is>
-          <t>TA builds the first arrow with the group and scribes each spoken arrow.  LOOP [Feedback Policy]: Voice = build/say the arrow [VF, ?] → Audience: name cause and consequence back; [R] once received → EVIDENCE: strip photo, same day [E: humanities — daily EFL; banks AQA UAS].</t>
+          <t>TA builds the first arrow with the group and scribes each spoken arrow.  LOOP [Feedback Policy]: Voice = build/say the arrow [VF, ?] → Audience: name cause and consequence back; [R] once received → EVIDENCE: strip photo, same day [E: humanities — daily evidence platform; banks AQA UAS].</t>
         </is>
       </c>
       <c r="J15" s="56" t="inlineStr">
